--- a/xls/square_12_tri3_22.xlsx
+++ b/xls/square_12_tri3_22.xlsx
@@ -482,13 +482,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.03947288977355486</v>
+        <v>-0.03947289060849494</v>
       </c>
       <c r="J22">
-        <v>-0.039884789976959094</v>
+        <v>-0.03988479064661679</v>
       </c>
       <c r="K22">
-        <v>3.715468988107356</v>
+        <v>3.7154689939115535</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -517,13 +517,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.005407255047001389</v>
+        <v>-0.005407255035796265</v>
       </c>
       <c r="J23">
-        <v>-0.0037575206112755847</v>
+        <v>-0.0037575206035392566</v>
       </c>
       <c r="K23">
-        <v>3.034548419938205</v>
+        <v>3.0345484196878996</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -552,13 +552,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-9.42062653203174e-5</v>
+        <v>-9.420626529171889e-5</v>
       </c>
       <c r="J24">
-        <v>-7.482400604260861e-5</v>
+        <v>-7.482400602621222e-5</v>
       </c>
       <c r="K24">
-        <v>2.3062501745753257</v>
+        <v>2.3062501743488237</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -587,13 +587,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.0002569116014114228</v>
+        <v>-0.00025691160150661</v>
       </c>
       <c r="J25">
-        <v>-0.0001834789965914496</v>
+        <v>-0.0001834789966542056</v>
       </c>
       <c r="K25">
-        <v>2.4456296080965334</v>
+        <v>2.445629608067936</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -622,13 +622,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.0001305019595298163</v>
+        <v>-0.00013050195955701852</v>
       </c>
       <c r="J26">
-        <v>-0.00010044093986619946</v>
+        <v>-0.00010044093988278973</v>
       </c>
       <c r="K26">
-        <v>2.356754315644601</v>
+        <v>2.3567543157220188</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.0001260931323460564</v>
+        <v>-0.0001260931323598503</v>
       </c>
       <c r="J27">
-        <v>-9.8620297080302e-5</v>
+        <v>-9.86202970894652e-5</v>
       </c>
       <c r="K27">
-        <v>2.3596290850280153</v>
+        <v>2.3596290852383475</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -692,13 +692,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.0001123748007083184</v>
+        <v>-0.00011237480071362357</v>
       </c>
       <c r="J28">
-        <v>-8.673693808891761e-5</v>
+        <v>-8.67369380920523e-5</v>
       </c>
       <c r="K28">
-        <v>2.3267480254858026</v>
+        <v>2.3267480255392528</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -727,13 +727,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.00011596270124906291</v>
+        <v>-0.00011596270124279311</v>
       </c>
       <c r="J29">
-        <v>-8.966153203463788e-5</v>
+        <v>-8.966153203077978e-5</v>
       </c>
       <c r="K29">
-        <v>2.3334232918494098</v>
+        <v>2.333423291886468</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -762,13 +762,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.00011147760159269233</v>
+        <v>-0.00011147760160392964</v>
       </c>
       <c r="J30">
-        <v>-8.703632061116186e-5</v>
+        <v>-8.703632061878158e-5</v>
       </c>
       <c r="K30">
-        <v>2.3300165137305475</v>
+        <v>2.3300165138021662</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -797,13 +797,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-6.780895812298991e-5</v>
+        <v>-6.780895812814986e-5</v>
       </c>
       <c r="J31">
-        <v>-4.851099823539173e-5</v>
+        <v>-4.851099823867081e-5</v>
       </c>
       <c r="K31">
-        <v>2.175083516531265</v>
+        <v>2.1750835166974767</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -832,13 +832,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.00015626558235321315</v>
+        <v>-0.00015626558235253788</v>
       </c>
       <c r="J32">
-        <v>-0.00011858897218524834</v>
+        <v>-0.00011858897218520011</v>
       </c>
       <c r="K32">
-        <v>2.384212361796201</v>
+        <v>2.384212361594108</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_22.xlsx
+++ b/xls/square_12_tri3_22.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>529</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>169</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>-1.4385816683091066</v>
+      </c>
+      <c r="J20">
+        <v>-1.7389583915557072</v>
+      </c>
+      <c r="K20">
+        <v>2.5916148298340187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>529</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>169</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>2646</v>
+      </c>
+      <c r="I21">
+        <v>-0.4516873731381407</v>
+      </c>
+      <c r="J21">
+        <v>-0.442382021932948</v>
+      </c>
+      <c r="K21">
+        <v>3.921606130589988</v>
+      </c>
+    </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>11</v>
